--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136994167</v>
       </c>
       <c r="B2" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136994167</v>
       </c>
       <c r="B2" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136994167</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106588</v>
+        <v>106590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 34200-2026 artfynd.xlsx
+++ b/artfynd/A 34200-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136994167</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136994215</v>
       </c>
       <c r="B3" t="n">
-        <v>106590</v>
+        <v>106594</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
